--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197245</v>
+        <v>120197211</v>
       </c>
       <c r="B3" t="n">
-        <v>79144</v>
+        <v>91863</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>6552907</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120197211</v>
+        <v>120197245</v>
       </c>
       <c r="B4" t="n">
-        <v>91863</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -945,7 +945,7 @@
         <v>6552907</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120198422</v>
+        <v>120201287</v>
       </c>
       <c r="B5" t="n">
-        <v>90582</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,27 +1027,32 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,12 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120198164</v>
+        <v>120197822</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
+        <v>90582</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,24 +1144,33 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
@@ -1174,7 +1183,7 @@
         <v>6552993</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120197822</v>
+        <v>120197423</v>
       </c>
       <c r="B7" t="n">
-        <v>90582</v>
+        <v>91863</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,33 +1265,24 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
@@ -1295,7 +1295,7 @@
         <v>6552993</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120199303</v>
+        <v>120198422</v>
       </c>
       <c r="B8" t="n">
-        <v>91863</v>
+        <v>90582</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         <v>6552984</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120201287</v>
+        <v>120198164</v>
       </c>
       <c r="B9" t="n">
-        <v>57326</v>
+        <v>90562</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,42 +1494,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R9" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120198388</v>
+        <v>120199303</v>
       </c>
       <c r="B10" t="n">
-        <v>79144</v>
+        <v>91863</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120197423</v>
+        <v>120198388</v>
       </c>
       <c r="B11" t="n">
-        <v>91863</v>
+        <v>79144</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R11" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120197245</v>
+        <v>120201287</v>
       </c>
       <c r="B4" t="n">
-        <v>79144</v>
+        <v>57326</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +915,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R4" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120201287</v>
+        <v>120197245</v>
       </c>
       <c r="B5" t="n">
-        <v>57326</v>
+        <v>79144</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,42 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R5" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120201287</v>
+        <v>120197245</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>79144</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,42 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R4" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197245</v>
+        <v>120201287</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
+        <v>57326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1027,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R5" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197263</v>
+        <v>120197211</v>
       </c>
       <c r="B2" t="n">
-        <v>79144</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659134</v>
+        <v>659194</v>
       </c>
       <c r="R2" t="n">
-        <v>6552993</v>
+        <v>6552907</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197211</v>
+        <v>120197245</v>
       </c>
       <c r="B3" t="n">
-        <v>91863</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>6552907</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120201287</v>
+        <v>120198422</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,32 +915,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197245</v>
+        <v>120197423</v>
       </c>
       <c r="B5" t="n">
-        <v>79144</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,37 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R5" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120197822</v>
+        <v>120198164</v>
       </c>
       <c r="B6" t="n">
-        <v>90582</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,33 +1144,24 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
@@ -1183,7 +1174,7 @@
         <v>6552993</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120197423</v>
+        <v>120197263</v>
       </c>
       <c r="B7" t="n">
-        <v>91863</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,7 +1286,7 @@
         <v>6552993</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120198422</v>
+        <v>120197822</v>
       </c>
       <c r="B8" t="n">
-        <v>90582</v>
+        <v>90600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,20 +1385,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R8" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,12 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120198164</v>
+        <v>120201287</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1494,37 +1489,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R9" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120199303</v>
+        <v>120198388</v>
       </c>
       <c r="B10" t="n">
-        <v>91863</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,7 +1636,7 @@
         <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120198388</v>
+        <v>120199303</v>
       </c>
       <c r="B11" t="n">
-        <v>79144</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
         <v>6552984</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197211</v>
+        <v>120198422</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R2" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197245</v>
+        <v>120197211</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +838,7 @@
         <v>6552907</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120198422</v>
+        <v>120197245</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,37 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R4" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120198422</v>
+        <v>120197245</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R2" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197211</v>
+        <v>120197263</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,37 +803,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R3" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120197245</v>
+        <v>120198164</v>
       </c>
       <c r="B4" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R4" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197423</v>
+        <v>120199303</v>
       </c>
       <c r="B5" t="n">
         <v>91881</v>
@@ -1056,13 +1051,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R5" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120198164</v>
+        <v>120201287</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,37 +1139,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R6" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120197263</v>
+        <v>120198422</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,13 +1280,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R7" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120201287</v>
+        <v>120197423</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1494,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R9" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120198388</v>
+        <v>120197211</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,37 +1606,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R10" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120199303</v>
+        <v>120198388</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1748,7 +1748,7 @@
         <v>6552984</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197245</v>
+        <v>120198164</v>
       </c>
       <c r="B2" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R2" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197263</v>
+        <v>120197423</v>
       </c>
       <c r="B3" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>6552993</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120198164</v>
+        <v>120198422</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R4" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120199303</v>
+        <v>120197245</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1032,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R5" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120201287</v>
+        <v>120197211</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,42 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R6" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120198422</v>
+        <v>120198388</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
         <v>6552984</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,12 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1478,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120197423</v>
+        <v>120199303</v>
       </c>
       <c r="B9" t="n">
         <v>91881</v>
@@ -1518,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R9" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120197211</v>
+        <v>120201287</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,37 +1601,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R10" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1702,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120198388</v>
+        <v>120197263</v>
       </c>
       <c r="B11" t="n">
         <v>79160</v>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R11" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120197211</v>
+        <v>120198388</v>
       </c>
       <c r="B6" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,37 +1144,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R6" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120198388</v>
+        <v>120197211</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,37 +1256,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R7" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120198164</v>
+        <v>120197423</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,7 +721,7 @@
         <v>6552993</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120197423</v>
+        <v>120198164</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,7 +833,7 @@
         <v>6552993</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120198422</v>
+        <v>120197822</v>
       </c>
       <c r="B4" t="n">
         <v>90600</v>
@@ -932,20 +932,29 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R4" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1020,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197245</v>
+        <v>120197263</v>
       </c>
       <c r="B5" t="n">
         <v>79160</v>
@@ -1052,17 +1056,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R5" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1095,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1105,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1240,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120197211</v>
+        <v>120198422</v>
       </c>
       <c r="B7" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,37 +1260,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R7" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1319,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1329,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120197822</v>
+        <v>120197245</v>
       </c>
       <c r="B8" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,46 +1377,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659134</v>
+        <v>659194</v>
       </c>
       <c r="R8" t="n">
-        <v>6552993</v>
+        <v>6552907</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120199303</v>
+        <v>120201287</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,27 +1489,32 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1519,7 +1524,7 @@
         <v>6552984</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120201287</v>
+        <v>120199303</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,32 +1606,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1636,7 +1636,7 @@
         <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120197263</v>
+        <v>120197211</v>
       </c>
       <c r="B11" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,37 +1718,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659134</v>
+        <v>659194</v>
       </c>
       <c r="R11" t="n">
-        <v>6552993</v>
+        <v>6552907</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197423</v>
+        <v>120197822</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>90600</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,24 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
@@ -721,7 +730,7 @@
         <v>6552993</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120198164</v>
+        <v>120199303</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +812,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +836,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R3" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +908,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120197822</v>
+        <v>120198422</v>
       </c>
       <c r="B4" t="n">
         <v>90600</v>
@@ -932,29 +941,20 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R4" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,7 +993,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,10 +1025,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197263</v>
+        <v>120197211</v>
       </c>
       <c r="B5" t="n">
-        <v>79160</v>
+        <v>91881</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,37 +1041,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659134</v>
+        <v>659194</v>
       </c>
       <c r="R5" t="n">
-        <v>6552993</v>
+        <v>6552907</v>
       </c>
       <c r="S5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,7 +1100,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1105,7 +1110,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,7 +1137,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120198388</v>
+        <v>120197263</v>
       </c>
       <c r="B6" t="n">
         <v>79160</v>
@@ -1172,13 +1177,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R6" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1212,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1222,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1244,10 +1249,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120198422</v>
+        <v>120197245</v>
       </c>
       <c r="B7" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1260,37 +1265,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R7" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1329,12 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120197245</v>
+        <v>120198164</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>90580</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,34 +1377,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R8" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120201287</v>
+        <v>120197423</v>
       </c>
       <c r="B9" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R9" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120199303</v>
+        <v>120198388</v>
       </c>
       <c r="B10" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1606,21 +1601,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1636,7 +1631,7 @@
         <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120197211</v>
+        <v>120201287</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,37 +1713,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R11" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120197822</v>
+        <v>120197423</v>
       </c>
       <c r="B2" t="n">
-        <v>90600</v>
+        <v>91881</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Söderängstorp, Söderängstorp, Srm</t>
@@ -730,7 +721,7 @@
         <v>6552993</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120199303</v>
+        <v>120198388</v>
       </c>
       <c r="B3" t="n">
-        <v>91881</v>
+        <v>79160</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,7 +833,7 @@
         <v>6552984</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120198422</v>
+        <v>120197245</v>
       </c>
       <c r="B4" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,37 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R4" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -993,12 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1137,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120197263</v>
+        <v>120198422</v>
       </c>
       <c r="B6" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1153,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1177,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R6" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1222,7 +1208,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120197245</v>
+        <v>120197822</v>
       </c>
       <c r="B7" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1265,37 +1256,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659194</v>
+        <v>659134</v>
       </c>
       <c r="R7" t="n">
-        <v>6552907</v>
+        <v>6552993</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120198164</v>
+        <v>120197263</v>
       </c>
       <c r="B8" t="n">
-        <v>90580</v>
+        <v>79160</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         <v>6552993</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120197423</v>
+        <v>120198164</v>
       </c>
       <c r="B9" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,21 +1489,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,7 +1519,7 @@
         <v>6552993</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:28</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120198388</v>
+        <v>120201287</v>
       </c>
       <c r="B10" t="n">
-        <v>79160</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,27 +1601,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
@@ -1631,7 +1636,7 @@
         <v>6552984</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1660,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120201287</v>
+        <v>120199303</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1713,32 +1718,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
@@ -1748,7 +1748,7 @@
         <v>6552984</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 16190-2024 artfynd.xlsx
+++ b/artfynd/A 16190-2024 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120198388</v>
+        <v>120197245</v>
       </c>
       <c r="B3" t="n">
         <v>79160</v>
@@ -823,17 +823,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söderängstorp, Söderängstorp, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R3" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120197245</v>
+        <v>120198388</v>
       </c>
       <c r="B4" t="n">
         <v>79160</v>
@@ -935,17 +935,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp, Söderängstorp, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R4" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120197211</v>
+        <v>120201287</v>
       </c>
       <c r="B5" t="n">
-        <v>91881</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,37 +1027,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rishopen, Rishopen, Srm</t>
+          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659194</v>
+        <v>659160</v>
       </c>
       <c r="R5" t="n">
-        <v>6552907</v>
+        <v>6552984</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1086,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:07</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120198422</v>
+        <v>120197263</v>
       </c>
       <c r="B6" t="n">
-        <v>90600</v>
+        <v>79160</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R6" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1198,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,12 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Stor tallticka med bohål under.</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1361,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120197263</v>
+        <v>120198422</v>
       </c>
       <c r="B8" t="n">
-        <v>79160</v>
+        <v>90600</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1377,21 +1377,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1401,13 +1401,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R8" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1446,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stor tallticka med bohål under.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120198164</v>
+        <v>120199303</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>91881</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,21 +1494,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5966</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1513,13 +1518,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>659134</v>
+        <v>659160</v>
       </c>
       <c r="R9" t="n">
-        <v>6552993</v>
+        <v>6552984</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1590,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120201287</v>
+        <v>120197211</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>91881</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1601,42 +1606,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5966</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Söderängstorp grustäkt, Kaggfjärden södra delen, Srm</t>
+          <t>Rishopen, Rishopen, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>659160</v>
+        <v>659194</v>
       </c>
       <c r="R10" t="n">
-        <v>6552984</v>
+        <v>6552907</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>10:07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120199303</v>
+        <v>120198164</v>
       </c>
       <c r="B11" t="n">
-        <v>91881</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,21 +1718,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1742,13 +1742,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>659160</v>
+        <v>659134</v>
       </c>
       <c r="R11" t="n">
-        <v>6552984</v>
+        <v>6552993</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
